--- a/markdown_generator/talks.xlsx
+++ b/markdown_generator/talks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkrishnamoorthy/Documents/ZZ_MyDocuments/Website/CurrWeb/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A32B6BBD-0562-BE4E-A315-5CFE2E21B279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1E2879-1273-B14D-88B3-2E767D173A84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5180" yWindow="1800" windowWidth="28040" windowHeight="17440" xr2:uid="{D55F21B5-A57E-9146-B0B7-3640A574C1AD}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="talks" localSheetId="0">Sheet1!$A$1:$H$5</definedName>
+    <definedName name="talks" localSheetId="0">Sheet1!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +39,7 @@
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
   <connection id="1" xr16:uid="{D8D0550F-4FEF-FA4A-AA0A-2023F49AFAB0}" name="talks" type="6" refreshedVersion="7" background="1" saveData="1">
-    <textPr codePage="10000" sourceFile="/Users/mkrishnamoorthy/Documents/ZZ_MyDocuments/Website/CurrWeb/markdown_generator/talks.tsv">
+    <textPr sourceFile="/Users/mkrishnamoorthy/Documents/ZZ_MyDocuments/Website/CurrWeb/markdown_generator/talks.tsv">
       <textFields count="8">
         <textField/>
         <textField/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="72">
   <si>
     <t>title</t>
   </si>
@@ -82,76 +82,201 @@
     <t>description</t>
   </si>
   <si>
-    <t>Talk 1 on Relevant Topic in Your Field</t>
-  </si>
-  <si>
     <t>Talk</t>
   </si>
   <si>
-    <t>talk-1</t>
-  </si>
-  <si>
-    <t>UC San Francisco, Department of Testing</t>
-  </si>
-  <si>
-    <t>San Francisco, California</t>
-  </si>
-  <si>
-    <t>This is a description of your talk, which is a markdown files that can be all markdown-ified like any other post. Yay markdown!</t>
-  </si>
-  <si>
-    <t>Tutorial 1 on Relevant Topic in Your Field</t>
-  </si>
-  <si>
-    <t>Tutorial</t>
-  </si>
-  <si>
-    <t>tutorial-1</t>
-  </si>
-  <si>
-    <t>UC-Berkeley Institute for Testing Science</t>
-  </si>
-  <si>
-    <t>Berkeley CA, USA</t>
-  </si>
-  <si>
-    <t>http://exampleurl.com</t>
-  </si>
-  <si>
-    <t>This is a description of your tutorial, note the different field in type. This is a markdown files that can be all markdown-ified like any other post. Yay markdown!</t>
-  </si>
-  <si>
-    <t>Talk 2 on Relevant Topic in Your Field</t>
-  </si>
-  <si>
-    <t>talk-2</t>
-  </si>
-  <si>
-    <t>London School of Testing</t>
-  </si>
-  <si>
-    <t>London, UK</t>
-  </si>
-  <si>
-    <t>http://example2.com</t>
-  </si>
-  <si>
-    <t>Conference Proceeding talk 3 on Relevant Topic in Your Field</t>
-  </si>
-  <si>
     <t>Conference proceedings talk</t>
   </si>
   <si>
-    <t>talk-3</t>
-  </si>
-  <si>
-    <t>Testing Institute of America 2014 Annual Conference</t>
-  </si>
-  <si>
-    <t>Los Angeles, CA</t>
-  </si>
-  <si>
-    <t>This is a description of your conference proceedings talk, note the different field in type. You can put anything in this field.</t>
+    <t>Apprentice for Event Generator Tuning</t>
+  </si>
+  <si>
+    <t>app21</t>
+  </si>
+  <si>
+    <t>25th International Conference on Computing in High Energy and Nuclear Physics</t>
+  </si>
+  <si>
+    <t>2021-05-20</t>
+  </si>
+  <si>
+    <t>Stochastic Optimization Algorithm based on Deterministic Approximations</t>
+  </si>
+  <si>
+    <t>soda21</t>
+  </si>
+  <si>
+    <t>Vienna, Austria (Online)</t>
+  </si>
+  <si>
+    <t>Paris, France (Online)</t>
+  </si>
+  <si>
+    <t>International Conference on Operations Research and Enterprise Systems</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>A Framework for Large-Scale Nonlinear Optimization</t>
+  </si>
+  <si>
+    <t>NLO20</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>SIAM Conference on Parallel Processing for Scientific Computing</t>
+  </si>
+  <si>
+    <t>2020-02-24</t>
+  </si>
+  <si>
+    <t>Bi-level Optimization for Design of Experiments</t>
+  </si>
+  <si>
+    <t>BLO19</t>
+  </si>
+  <si>
+    <t>INFORMS Annual Meeting</t>
+  </si>
+  <si>
+    <t>2019-10-20</t>
+  </si>
+  <si>
+    <t>Optimization based on White-Box Deterministic Approximations: Models, Algorithms, and Application to Service Networks</t>
+  </si>
+  <si>
+    <t>Argonne National Laboratory</t>
+  </si>
+  <si>
+    <t>Lemont, IL</t>
+  </si>
+  <si>
+    <t>SODA18</t>
+  </si>
+  <si>
+    <t>2018-06-20</t>
+  </si>
+  <si>
+    <t>Service Networks: Stochastic Optimization based on Deterministic Approximations and  Repository of Performance Models</t>
+  </si>
+  <si>
+    <t>Invited talk</t>
+  </si>
+  <si>
+    <t>SN17</t>
+  </si>
+  <si>
+    <t>Doctoral Candidate Student Presentations at the 29𝑡h
+International Conference on Tools for Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>2017-11-06</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>Manufacturing and Contract Service Networks: Composition, Optimization and Tradeoff Analysis based on a Reusable Repository of Performance Models</t>
+  </si>
+  <si>
+    <t>MCSN17</t>
+  </si>
+  <si>
+    <t>IEEE International Conference
+on Big Data</t>
+  </si>
+  <si>
+    <t>20217-12-12</t>
+  </si>
+  <si>
+    <t>A System and Architecture for Reusable Abstractions of Manufacturing Processes</t>
+  </si>
+  <si>
+    <t>RAMP16</t>
+  </si>
+  <si>
+    <t>IEEE
+International Conference on Big Data</t>
+  </si>
+  <si>
+    <t>Washington DC</t>
+  </si>
+  <si>
+    <t>20216-12-06</t>
+  </si>
+  <si>
+    <t>Efficient Decision Support System for Discrete Manufacturing Processes</t>
+  </si>
+  <si>
+    <t>DSS16</t>
+  </si>
+  <si>
+    <t>Computer Science PhD Symposium, George Mason University</t>
+  </si>
+  <si>
+    <t>20216-12-15</t>
+  </si>
+  <si>
+    <t>Fairfax, VA</t>
+  </si>
+  <si>
+    <t>Analysis and Optimization in Smart Manufacturing based on a Reusable Knowledge Base for
+Process Performance Models</t>
+  </si>
+  <si>
+    <t>Santa Clara, CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> IEEE International Conference on Big Data</t>
+  </si>
+  <si>
+    <t>SM15</t>
+  </si>
+  <si>
+    <t>2015-10-30</t>
+  </si>
+  <si>
+    <t>Temporal manufacturing query language (tMQL) for domain specific composition, what-if analysis, and optimization of manufacturing processes with inventories</t>
+  </si>
+  <si>
+    <t>Richmond, VA</t>
+  </si>
+  <si>
+    <t>INFORMS Computing
+Society Conference</t>
+  </si>
+  <si>
+    <t>TMQL15</t>
+  </si>
+  <si>
+    <t>Workshop talk</t>
+  </si>
+  <si>
+    <t>2015-01-12</t>
+  </si>
+  <si>
+    <t>SODA15</t>
+  </si>
+  <si>
+    <t>Optimizing Stochastic Temporal Manufacturing Processes with Inventories: An Efficient  Heuristic Algorithm Based on Deterministic Approximations</t>
+  </si>
+  <si>
+    <t>Tree prune &amp; decorator: An efficient tool for selecting and annotating data from a biased genetic database</t>
+  </si>
+  <si>
+    <t>Los Alamos, NM</t>
+  </si>
+  <si>
+    <t>TP10</t>
+  </si>
+  <si>
+    <t>Theoretical Biology and Biophysics Seminar, Los Alamos National Laboratory</t>
+  </si>
+  <si>
+    <t>2010-05-10</t>
   </si>
 </sst>
 </file>
@@ -187,9 +312,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,14 +637,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26C645E-A7F1-114D-9D33-32D0ACC733A0}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.1640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="21.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="80.6640625" bestFit="1" customWidth="1"/>
@@ -531,10 +660,10 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -549,25 +678,22 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1">
-        <v>40969</v>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -575,77 +701,243 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
         <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="1">
-        <v>41334</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
         <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="1">
-        <v>41671</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="1">
-        <v>41699</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H5" t="s">
+      <c r="E6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/markdown_generator/talks.xlsx
+++ b/markdown_generator/talks.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkrishnamoorthy/Documents/ZZ_MyDocuments/Website/CurrWeb/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1E2879-1273-B14D-88B3-2E767D173A84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6930D7E3-CEDE-8646-BB81-CB26EF2B1D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5180" yWindow="1800" windowWidth="28040" windowHeight="17440" xr2:uid="{D55F21B5-A57E-9146-B0B7-3640A574C1AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="talks" localSheetId="0">Sheet1!$A$1:$H$2</definedName>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="72">
   <si>
     <t>title</t>
   </si>
@@ -681,7 +682,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -701,7 +702,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -761,7 +762,7 @@
         <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
         <v>32</v>
@@ -781,7 +782,7 @@
         <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
         <v>36</v>
@@ -801,7 +802,7 @@
         <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
         <v>41</v>
@@ -821,7 +822,7 @@
         <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
         <v>45</v>
@@ -841,7 +842,7 @@
         <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
         <v>50</v>
@@ -861,7 +862,7 @@
         <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
         <v>57</v>
@@ -881,7 +882,7 @@
         <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
         <v>62</v>
@@ -901,7 +902,7 @@
         <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
         <v>65</v>
@@ -940,4 +941,79 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B206D6C1-C276-3E44-95E0-186E4CAB45E0}">
+  <dimension ref="A1:A13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/markdown_generator/talks.xlsx
+++ b/markdown_generator/talks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkrishnamoorthy/Documents/ZZ_MyDocuments/Website/CurrWeb/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6930D7E3-CEDE-8646-BB81-CB26EF2B1D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA5327B-0678-D04D-A9CA-F7EFD0C30964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5180" yWindow="1800" windowWidth="28040" windowHeight="17440" xr2:uid="{D55F21B5-A57E-9146-B0B7-3640A574C1AD}"/>
   </bookViews>
@@ -170,10 +170,6 @@
     <t>SN17</t>
   </si>
   <si>
-    <t>Doctoral Candidate Student Presentations at the 29𝑡h
-International Conference on Tools for Artificial Intelligence</t>
-  </si>
-  <si>
     <t>2017-11-06</t>
   </si>
   <si>
@@ -278,6 +274,10 @@
   </si>
   <si>
     <t>2010-05-10</t>
+  </si>
+  <si>
+    <t>Doctoral Candidate Student Presentations at the 29th
+International Conference on Tools for Artificial Intelligence</t>
   </si>
 </sst>
 </file>
@@ -777,7 +777,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -787,154 +787,154 @@
       <c r="C7" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" t="s">
         <v>38</v>
-      </c>
-      <c r="F7" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
         <v>40</v>
       </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
         <v>44</v>
       </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" t="s">
         <v>46</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
         <v>49</v>
       </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" t="s">
         <v>59</v>
-      </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" t="s">
         <v>67</v>
-      </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F14" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1000,7 +1000,7 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">

--- a/markdown_generator/talks.xlsx
+++ b/markdown_generator/talks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkrishnamoorthy/Documents/ZZ_MyDocuments/Website/CurrWeb/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA5327B-0678-D04D-A9CA-F7EFD0C30964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A55EEC3-505C-414C-B192-50FFE4D808C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5180" yWindow="1800" windowWidth="28040" windowHeight="17440" xr2:uid="{D55F21B5-A57E-9146-B0B7-3640A574C1AD}"/>
   </bookViews>
@@ -186,9 +186,6 @@
 on Big Data</t>
   </si>
   <si>
-    <t>20217-12-12</t>
-  </si>
-  <si>
     <t>A System and Architecture for Reusable Abstractions of Manufacturing Processes</t>
   </si>
   <si>
@@ -202,9 +199,6 @@
     <t>Washington DC</t>
   </si>
   <si>
-    <t>20216-12-06</t>
-  </si>
-  <si>
     <t>Efficient Decision Support System for Discrete Manufacturing Processes</t>
   </si>
   <si>
@@ -212,9 +206,6 @@
   </si>
   <si>
     <t>Computer Science PhD Symposium, George Mason University</t>
-  </si>
-  <si>
-    <t>20216-12-15</t>
   </si>
   <si>
     <t>Fairfax, VA</t>
@@ -278,6 +269,15 @@
   <si>
     <t>Doctoral Candidate Student Presentations at the 29th
 International Conference on Tools for Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>2017-12-12</t>
+  </si>
+  <si>
+    <t>2016-12-06</t>
+  </si>
+  <si>
+    <t>2016-12-15</t>
   </si>
 </sst>
 </file>
@@ -788,7 +788,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>37</v>
@@ -811,7 +811,7 @@
         <v>41</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="F8" t="s">
         <v>38</v>
@@ -819,122 +819,122 @@
     </row>
     <row r="9" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
         <v>43</v>
       </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" t="s">
         <v>45</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="E10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
         <v>53</v>
       </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>56</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
         <v>58</v>
       </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>61</v>
-      </c>
       <c r="D12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="E14" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1000,7 +1000,7 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
